--- a/data/trans_orig/Hacinamiento_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/Hacinamiento_R-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>707</t>
+          <t>530</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5844</t>
+          <t>5245</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3888</t>
+          <t>3681</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1106</t>
+          <t>1127</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6642</t>
+          <t>7034</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>7,11%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>41863</t>
+          <t>42462</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>47000</t>
+          <t>47177</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>89,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>47276</t>
+          <t>47483</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>92229</t>
+          <t>91837</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>97765</t>
+          <t>97744</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,86%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2490</t>
+          <t>2508</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9473</t>
+          <t>9032</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3855</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12289</t>
+          <t>12599</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7729</t>
+          <t>7589</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18703</t>
+          <t>18908</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,24%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>58414</t>
+          <t>58855</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>65397</t>
+          <t>65379</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,05%</t>
+          <t>86,7%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>52645</t>
+          <t>52335</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>61079</t>
+          <t>60934</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,08%</t>
+          <t>80,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>114117</t>
+          <t>113912</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>125091</t>
+          <t>125231</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>85,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>94,29%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1487</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8811</t>
+          <t>8993</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3697</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10553</t>
+          <t>11224</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6440</t>
+          <t>6578</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16222</t>
+          <t>16789</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,66%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>55886</t>
+          <t>55704</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>63210</t>
+          <t>62674</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>86,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>57349</t>
+          <t>56678</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>64205</t>
+          <t>64797</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>83,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>116378</t>
+          <t>115811</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>126160</t>
+          <t>126022</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>87,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,04%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2045</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9017</t>
+          <t>8705</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1687</t>
+          <t>2179</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9655</t>
+          <t>8963</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4892</t>
+          <t>5385</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16495</t>
+          <t>17227</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>12,34%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>57037</t>
+          <t>57349</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>64009</t>
+          <t>64403</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,35%</t>
+          <t>86,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>63861</t>
+          <t>64553</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>71829</t>
+          <t>71337</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,87%</t>
+          <t>87,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>123074</t>
+          <t>122342</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>134677</t>
+          <t>134184</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,18%</t>
+          <t>87,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,14%</t>
         </is>
       </c>
     </row>
@@ -2110,7 +2110,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4196</t>
+          <t>4140</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>43,98%</t>
+          <t>43,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3522</t>
+          <t>2879</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>696</t>
+          <t>690</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5561</t>
+          <t>5037</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>24,05%</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5345</t>
+          <t>5401</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>56,02%</t>
+          <t>56,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7877</t>
+          <t>8520</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>69,1%</t>
+          <t>74,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>15380</t>
+          <t>15904</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>20245</t>
+          <t>20251</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>73,44%</t>
+          <t>75,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,7%</t>
         </is>
       </c>
     </row>
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6307</t>
+          <t>6370</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3691</t>
+          <t>3325</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1372</t>
+          <t>1361</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7559</t>
+          <t>7646</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,73%</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>40352</t>
+          <t>40289</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>86,35%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>48580</t>
+          <t>48946</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>91370</t>
+          <t>91283</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>97557</t>
+          <t>97568</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,62%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4886</t>
+          <t>4809</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14055</t>
+          <t>14006</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5961</t>
+          <t>6025</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>15037</t>
+          <t>16133</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>13155</t>
+          <t>12478</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>26276</t>
+          <t>25787</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,65%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>96591</t>
+          <t>96640</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>105760</t>
+          <t>105837</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>87,3%</t>
+          <t>87,34%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>95749</t>
+          <t>94653</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>104825</t>
+          <t>104761</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>86,43%</t>
+          <t>85,44%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>195157</t>
+          <t>195646</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>208278</t>
+          <t>208955</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>88,35%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>94,36%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1393</t>
+          <t>1285</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7866</t>
+          <t>7855</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>7165</t>
+          <t>7050</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>17356</t>
+          <t>17123</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>11030</t>
+          <t>10510</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>22932</t>
+          <t>23153</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,47%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>81186</t>
+          <t>81197</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>87659</t>
+          <t>87767</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>79221</t>
+          <t>79454</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>89412</t>
+          <t>89527</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>82,03%</t>
+          <t>82,27%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,7%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>162697</t>
+          <t>162476</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>174599</t>
+          <t>175119</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>87,65%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>94,34%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>25409</t>
+          <t>24919</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>43683</t>
+          <t>42812</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>33619</t>
+          <t>32699</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>53681</t>
+          <t>53374</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>61797</t>
+          <t>61541</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>89101</t>
+          <t>88920</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,63%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>458560</t>
+          <t>459431</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>476834</t>
+          <t>477324</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,48%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>474868</t>
+          <t>475175</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>494930</t>
+          <t>495850</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>89,84%</t>
+          <t>89,9%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>941691</t>
+          <t>941872</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>968995</t>
+          <t>969251</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>91,37%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>94,03%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1421</t>
+          <t>1228</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7455</t>
+          <t>7150</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2491</t>
+          <t>2406</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9972</t>
+          <t>10314</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4939</t>
+          <t>5006</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14045</t>
+          <t>14631</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>23,06%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17902</t>
+          <t>18207</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23936</t>
+          <t>24129</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>70,6%</t>
+          <t>71,8%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28108</t>
+          <t>27766</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>35589</t>
+          <t>35674</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,81%</t>
+          <t>72,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>49393</t>
+          <t>48807</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>58499</t>
+          <t>58432</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,86%</t>
+          <t>76,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>92,11%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1302</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7596</t>
+          <t>7442</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2743</t>
+          <t>3125</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10552</t>
+          <t>10964</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5359</t>
+          <t>5672</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15033</t>
+          <t>15854</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>14,0%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>46790</t>
+          <t>46944</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>53084</t>
+          <t>53120</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>86,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>48334</t>
+          <t>47922</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>56143</t>
+          <t>55761</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,08%</t>
+          <t>81,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>98239</t>
+          <t>97418</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>107913</t>
+          <t>107600</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,73%</t>
+          <t>86,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>94,99%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>895</t>
+          <t>731</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7846</t>
+          <t>6355</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>722</t>
+          <t>731</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7133</t>
+          <t>7540</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2843</t>
+          <t>2397</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11239</t>
+          <t>11161</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,91%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>44867</t>
+          <t>46358</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>51818</t>
+          <t>51982</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>87,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>52801</t>
+          <t>52394</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>59212</t>
+          <t>59203</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,1%</t>
+          <t>87,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>101408</t>
+          <t>101486</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>109804</t>
+          <t>110250</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,02%</t>
+          <t>90,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,87%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>843</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6646</t>
+          <t>6712</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2438</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11155</t>
+          <t>10997</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4056</t>
+          <t>4191</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14491</t>
+          <t>14257</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,56%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>43034</t>
+          <t>42968</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>48837</t>
+          <t>49680</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,62%</t>
+          <t>86,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>44317</t>
+          <t>44475</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>53034</t>
+          <t>53169</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,89%</t>
+          <t>80,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>90661</t>
+          <t>90895</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>101096</t>
+          <t>100961</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,22%</t>
+          <t>86,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,01%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>659</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5686</t>
+          <t>5063</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1580</t>
+          <t>1447</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7840</t>
+          <t>7977</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>32,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2980</t>
+          <t>2968</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10969</t>
+          <t>10670</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>25,0%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12357</t>
+          <t>12980</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17386</t>
+          <t>17384</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>68,49%</t>
+          <t>71,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>16790</t>
+          <t>16653</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23050</t>
+          <t>23183</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>68,17%</t>
+          <t>67,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>31704</t>
+          <t>32003</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>39693</t>
+          <t>39705</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>74,3%</t>
+          <t>75,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>93,04%</t>
         </is>
       </c>
     </row>
@@ -5776,7 +5776,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5055</t>
+          <t>4907</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>728</t>
+          <t>715</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6141</t>
+          <t>5657</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1432</t>
+          <t>1406</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8288</t>
+          <t>8195</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,71%</t>
         </is>
       </c>
     </row>
@@ -5884,7 +5884,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>39487</t>
+          <t>39635</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>88,98%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>43392</t>
+          <t>43876</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>48805</t>
+          <t>48818</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,6%</t>
+          <t>88,58%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>85787</t>
+          <t>85880</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>92643</t>
+          <t>92669</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>91,29%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,51%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>12732</t>
+          <t>12477</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>25485</t>
+          <t>26022</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8660</t>
+          <t>8648</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>21486</t>
+          <t>21256</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>24547</t>
+          <t>24257</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>43475</t>
+          <t>43229</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,13%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>91219</t>
+          <t>90682</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>103972</t>
+          <t>104227</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>78,16%</t>
+          <t>77,7%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>89,31%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>100291</t>
+          <t>100521</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>113117</t>
+          <t>113129</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>82,36%</t>
+          <t>82,55%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>195005</t>
+          <t>195251</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>213933</t>
+          <t>214223</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>81,77%</t>
+          <t>81,87%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>89,83%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8617</t>
+          <t>9088</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>19578</t>
+          <t>19808</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5280</t>
+          <t>4838</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>14529</t>
+          <t>14563</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>16196</t>
+          <t>16283</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>31163</t>
+          <t>30791</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,52%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>95961</t>
+          <t>95731</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>106922</t>
+          <t>106451</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>83,06%</t>
+          <t>82,86%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>115939</t>
+          <t>115905</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>125188</t>
+          <t>125630</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>214844</t>
+          <t>215216</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>229811</t>
+          <t>229724</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>87,48%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,38%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>38389</t>
+          <t>39011</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>61454</t>
+          <t>60340</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>39493</t>
+          <t>38238</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>62706</t>
+          <t>61357</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>83350</t>
+          <t>83051</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>114106</t>
+          <t>113810</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,2%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>415511</t>
+          <t>416625</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>438576</t>
+          <t>437954</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>87,12%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>91,82%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>476075</t>
+          <t>477424</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>499288</t>
+          <t>500543</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>88,61%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>901640</t>
+          <t>901936</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>932396</t>
+          <t>932695</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>88,8%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>91,82%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3560</t>
+          <t>3384</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11755</t>
+          <t>12690</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>27,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5896</t>
+          <t>6129</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15452</t>
+          <t>15893</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11283</t>
+          <t>11133</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24189</t>
+          <t>24669</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>25,33%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>33631</t>
+          <t>32696</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>41826</t>
+          <t>42002</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>74,1%</t>
+          <t>72,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>36542</t>
+          <t>36101</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>46098</t>
+          <t>45865</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>70,28%</t>
+          <t>69,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,66%</t>
+          <t>88,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>73191</t>
+          <t>72711</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>86097</t>
+          <t>86247</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,16%</t>
+          <t>74,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>88,57%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6373</t>
+          <t>6537</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16149</t>
+          <t>16700</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3296</t>
+          <t>3869</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11521</t>
+          <t>12193</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11523</t>
+          <t>12012</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>24619</t>
+          <t>24727</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,41%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>54553</t>
+          <t>54002</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>64329</t>
+          <t>64165</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>77,16%</t>
+          <t>76,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>90,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>68474</t>
+          <t>67802</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>76699</t>
+          <t>76126</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>84,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>126078</t>
+          <t>125970</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>139174</t>
+          <t>138685</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,66%</t>
+          <t>83,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,03%</t>
         </is>
       </c>
     </row>
@@ -8070,7 +8070,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5927</t>
+          <t>5852</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8085,7 +8085,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>726</t>
+          <t>976</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6995</t>
+          <t>7534</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2096</t>
+          <t>2173</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10331</t>
+          <t>10877</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,75%</t>
         </is>
       </c>
     </row>
@@ -8178,7 +8178,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>52186</t>
+          <t>52261</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -8193,7 +8193,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,8%</t>
+          <t>89,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>59182</t>
+          <t>58643</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>65451</t>
+          <t>65201</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,43%</t>
+          <t>88,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>113958</t>
+          <t>113412</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>122193</t>
+          <t>122116</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,25%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4201</t>
+          <t>4266</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12580</t>
+          <t>12960</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2895</t>
+          <t>2980</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11260</t>
+          <t>10723</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8381</t>
+          <t>8436</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>19755</t>
+          <t>19815</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>21,36%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>32533</t>
+          <t>32153</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>40912</t>
+          <t>40847</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,12%</t>
+          <t>71,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>90,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>36390</t>
+          <t>36927</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>44755</t>
+          <t>44670</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,37%</t>
+          <t>77,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>73008</t>
+          <t>72948</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>84382</t>
+          <t>84327</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,7%</t>
+          <t>78,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>90,91%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>744</t>
+          <t>765</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6665</t>
+          <t>6966</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>593</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5056</t>
+          <t>5533</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2258</t>
+          <t>2148</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9661</t>
+          <t>9242</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>13,61%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>25710</t>
+          <t>25409</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>31631</t>
+          <t>31610</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>79,41%</t>
+          <t>78,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>30460</t>
+          <t>29983</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>35516</t>
+          <t>34923</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,76%</t>
+          <t>84,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>58229</t>
+          <t>58648</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>65632</t>
+          <t>65742</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,77%</t>
+          <t>86,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,84%</t>
         </is>
       </c>
     </row>
@@ -9099,7 +9099,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4002</t>
+          <t>4402</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9169,7 +9169,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3867</t>
+          <t>3664</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9184,7 +9184,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,25%</t>
         </is>
       </c>
     </row>
@@ -9207,7 +9207,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>23281</t>
+          <t>22881</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -9222,7 +9222,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>85,33%</t>
+          <t>83,87%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -9277,7 +9277,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>54772</t>
+          <t>54975</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -9292,7 +9292,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1317</t>
+          <t>1312</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>8200</t>
+          <t>7805</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9457,7 +9457,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2679</t>
+          <t>2598</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>10829</t>
+          <t>10465</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5231</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>15215</t>
+          <t>15121</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,45%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>107860</t>
+          <t>108255</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>114743</t>
+          <t>114748</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,7 +9565,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>107648</t>
+          <t>108012</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>115798</t>
+          <t>115879</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>219322</t>
+          <t>219416</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>229306</t>
+          <t>229180</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,72%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6388</t>
+          <t>6395</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>16448</t>
+          <t>15904</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9800,7 +9800,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1364</t>
+          <t>1377</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7886</t>
+          <t>7981</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>9535</t>
+          <t>9850</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>21314</t>
+          <t>21153</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,87%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>113205</t>
+          <t>113749</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>123265</t>
+          <t>123258</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,7 +9908,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>87,31%</t>
+          <t>87,73%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>131337</t>
+          <t>131242</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>137859</t>
+          <t>137846</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>247562</t>
+          <t>247723</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>259341</t>
+          <t>259026</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,34%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>34963</t>
+          <t>34721</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>56558</t>
+          <t>55716</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>28904</t>
+          <t>28628</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>49272</t>
+          <t>48785</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>70008</t>
+          <t>67923</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>99045</t>
+          <t>96114</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,78%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>468127</t>
+          <t>468969</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>489722</t>
+          <t>489964</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>89,38%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>521115</t>
+          <t>521602</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>541483</t>
+          <t>541759</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>91,45%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>996027</t>
+          <t>998958</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1025064</t>
+          <t>1027149</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,8%</t>
         </is>
       </c>
     </row>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>785</t>
+          <t>744</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7629</t>
+          <t>7023</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2430</t>
+          <t>2465</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12206</t>
+          <t>12684</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4113</t>
+          <t>4018</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15129</t>
+          <t>15058</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,86%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>65653</t>
+          <t>66259</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>72497</t>
+          <t>72538</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>67160</t>
+          <t>66682</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>76936</t>
+          <t>76901</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,62%</t>
+          <t>84,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>137519</t>
+          <t>137590</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>148535</t>
+          <t>148630</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,37%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1570</t>
+          <t>1528</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10785</t>
+          <t>10144</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8369</t>
+          <t>8530</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22583</t>
+          <t>22667</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11679</t>
+          <t>11653</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>29628</t>
+          <t>29734</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,65%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>116869</t>
+          <t>117510</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>126084</t>
+          <t>126126</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>92,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>105013</t>
+          <t>104929</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>119227</t>
+          <t>119066</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,3%</t>
+          <t>82,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>225622</t>
+          <t>225516</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>243571</t>
+          <t>243597</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>88,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,43%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6137</t>
+          <t>5607</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15541</t>
+          <t>14168</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3041</t>
+          <t>2800</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11245</t>
+          <t>10720</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9636</t>
+          <t>10342</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21755</t>
+          <t>22647</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>18,18%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>42258</t>
+          <t>43631</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>51662</t>
+          <t>52192</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>73,11%</t>
+          <t>75,49%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>90,3%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>55537</t>
+          <t>56062</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>63741</t>
+          <t>63982</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,16%</t>
+          <t>83,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>102826</t>
+          <t>101934</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>114945</t>
+          <t>114239</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,54%</t>
+          <t>81,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>91,7%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>492</t>
+          <t>626</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7798</t>
+          <t>7745</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>979</t>
+          <t>908</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10526</t>
+          <t>9686</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2591</t>
+          <t>2176</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14571</t>
+          <t>13885</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,43%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>61346</t>
+          <t>61399</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>68652</t>
+          <t>68518</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,72%</t>
+          <t>88,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>67608</t>
+          <t>68448</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>77155</t>
+          <t>77226</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,53%</t>
+          <t>87,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>132707</t>
+          <t>133393</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>144687</t>
+          <t>145102</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,52%</t>
         </is>
       </c>
     </row>
@@ -12079,7 +12079,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2392</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12094,7 +12094,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12114,7 +12114,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7516</t>
+          <t>7336</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12129,7 +12129,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12149,7 +12149,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8122</t>
+          <t>8102</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12164,7 +12164,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,77%</t>
         </is>
       </c>
     </row>
@@ -12187,7 +12187,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>32121</t>
+          <t>31760</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -12202,7 +12202,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>92,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -12222,7 +12222,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>33203</t>
+          <t>33383</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -12237,7 +12237,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,54%</t>
+          <t>81,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -12257,7 +12257,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>67110</t>
+          <t>67130</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -12272,7 +12272,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>388</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4390</t>
+          <t>4543</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4174</t>
+          <t>4098</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>14663</t>
+          <t>14665</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,7 +12467,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5412</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>16957</t>
+          <t>17295</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>17,02%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>41042</t>
+          <t>40889</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>45051</t>
+          <t>45044</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>41523</t>
+          <t>41521</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>52012</t>
+          <t>52088</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12585,7 +12585,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,71%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>84661</t>
+          <t>84323</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>96206</t>
+          <t>96344</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>83,31%</t>
+          <t>82,98%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,81%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9012</t>
+          <t>8932</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>21731</t>
+          <t>21018</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>12806</t>
+          <t>13520</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>28922</t>
+          <t>29896</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>25564</t>
+          <t>26128</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>44225</t>
+          <t>46161</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>16,51%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>102356</t>
+          <t>103069</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>115075</t>
+          <t>115155</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>82,49%</t>
+          <t>83,06%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>126595</t>
+          <t>125621</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>142711</t>
+          <t>141997</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>81,4%</t>
+          <t>80,78%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>235379</t>
+          <t>233443</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>254040</t>
+          <t>253476</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>84,18%</t>
+          <t>83,49%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>90,66%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>936</t>
+          <t>1219</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6637</t>
+          <t>7722</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>359</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4701</t>
+          <t>5242</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2098</t>
+          <t>2223</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>9177</t>
+          <t>9207</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,24%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>121742</t>
+          <t>120657</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>127443</t>
+          <t>127160</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>93,99%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>151286</t>
+          <t>150745</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>155987</t>
+          <t>155628</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,77%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>275189</t>
+          <t>275159</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>282268</t>
+          <t>282143</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,22%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>29988</t>
+          <t>29505</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>51536</t>
+          <t>50292</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>49592</t>
+          <t>49117</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>77792</t>
+          <t>77960</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>85519</t>
+          <t>86545</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>120247</t>
+          <t>123106</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,67%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>608753</t>
+          <t>609997</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>630301</t>
+          <t>630784</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>682496</t>
+          <t>682328</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>710696</t>
+          <t>711171</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>89,77%</t>
+          <t>89,75%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1300330</t>
+          <t>1297471</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1335058</t>
+          <t>1334032</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>93,91%</t>
         </is>
       </c>
     </row>
